--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130158948</v>
+        <v>130158947</v>
       </c>
       <c r="B6" t="n">
-        <v>91635</v>
+        <v>56922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,41 +1207,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499602</v>
+        <v>499666</v>
       </c>
       <c r="R6" t="n">
-        <v>7029397</v>
+        <v>7029380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1287,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
+          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,33 +1296,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1331,7 +1319,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130158949</v>
+        <v>130158948</v>
       </c>
       <c r="B7" t="n">
         <v>91635</v>
@@ -1373,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499788</v>
+        <v>499602</v>
       </c>
       <c r="R7" t="n">
-        <v>7029153</v>
+        <v>7029397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,7 +1401,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
+          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,12 +1431,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1466,10 +1454,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130158947</v>
+        <v>130158949</v>
       </c>
       <c r="B8" t="n">
-        <v>56922</v>
+        <v>91635</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,50 +1465,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499666</v>
+        <v>499788</v>
       </c>
       <c r="R8" t="n">
-        <v>7029380</v>
+        <v>7029153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1557,7 +1536,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
+          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,12 +1545,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158953</v>
       </c>
       <c r="B2" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130158954</v>
       </c>
       <c r="B3" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>130158951</v>
       </c>
       <c r="B4" t="n">
-        <v>98737</v>
+        <v>98739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130158952</v>
       </c>
       <c r="B5" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>130158948</v>
       </c>
       <c r="B7" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>130158949</v>
       </c>
       <c r="B8" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1589,27 +1589,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130158946</v>
+        <v>130158941</v>
       </c>
       <c r="B9" t="n">
-        <v>57845</v>
+        <v>57738</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,33 +1617,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499792</v>
+        <v>499782</v>
       </c>
       <c r="R9" t="n">
-        <v>7029121</v>
+        <v>7029157</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1680,7 +1672,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
+          <t>Grova äldre hackspår i en levande gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,7 +1686,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1712,27 +1724,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130158941</v>
+        <v>130158946</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1740,25 +1752,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499782</v>
+        <v>499792</v>
       </c>
       <c r="R10" t="n">
-        <v>7029157</v>
+        <v>7029121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1795,7 +1815,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Grova äldre hackspår i en levande gran.</t>
+          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,27 +1829,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
         <v>130158944</v>
       </c>
       <c r="B11" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158953</v>
       </c>
       <c r="B2" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130158954</v>
       </c>
       <c r="B3" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>130158951</v>
       </c>
       <c r="B4" t="n">
-        <v>98739</v>
+        <v>98826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130158952</v>
       </c>
       <c r="B5" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130158947</v>
+        <v>130158948</v>
       </c>
       <c r="B6" t="n">
-        <v>56922</v>
+        <v>91724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,50 +1207,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499666</v>
+        <v>499602</v>
       </c>
       <c r="R6" t="n">
-        <v>7029380</v>
+        <v>7029397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1278,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
+          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,12 +1287,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,10 +1331,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130158948</v>
+        <v>130158947</v>
       </c>
       <c r="B7" t="n">
-        <v>91637</v>
+        <v>57007</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,41 +1342,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499602</v>
+        <v>499666</v>
       </c>
       <c r="R7" t="n">
-        <v>7029397</v>
+        <v>7029380</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,7 +1422,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
+          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,33 +1431,12 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1457,7 +1457,7 @@
         <v>130158949</v>
       </c>
       <c r="B8" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>130158941</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>130158946</v>
       </c>
       <c r="B10" t="n">
-        <v>57845</v>
+        <v>57930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>130158944</v>
       </c>
       <c r="B11" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>130158942</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>130158940</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>130158960</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>130158961</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>130158962</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>130158963</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130158948</v>
+        <v>130158947</v>
       </c>
       <c r="B6" t="n">
-        <v>91724</v>
+        <v>57007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,41 +1207,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499602</v>
+        <v>499666</v>
       </c>
       <c r="R6" t="n">
-        <v>7029397</v>
+        <v>7029380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1287,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
+          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,33 +1296,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1331,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130158947</v>
+        <v>130158948</v>
       </c>
       <c r="B7" t="n">
-        <v>57007</v>
+        <v>91724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,50 +1330,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499666</v>
+        <v>499602</v>
       </c>
       <c r="R7" t="n">
-        <v>7029380</v>
+        <v>7029397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1422,7 +1401,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
+          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,12 +1410,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1589,27 +1589,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130158941</v>
+        <v>130158946</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,25 +1617,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499782</v>
+        <v>499792</v>
       </c>
       <c r="R9" t="n">
-        <v>7029157</v>
+        <v>7029121</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1672,7 +1680,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Grova äldre hackspår i en levande gran.</t>
+          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,27 +1694,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1724,27 +1712,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130158946</v>
+        <v>130158941</v>
       </c>
       <c r="B10" t="n">
-        <v>57930</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1752,33 +1740,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499792</v>
+        <v>499782</v>
       </c>
       <c r="R10" t="n">
-        <v>7029121</v>
+        <v>7029157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1815,7 +1795,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
+          <t>Grova äldre hackspår i en levande gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1829,7 +1809,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130158947</v>
+        <v>130158948</v>
       </c>
       <c r="B6" t="n">
-        <v>57007</v>
+        <v>91724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,50 +1207,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499666</v>
+        <v>499602</v>
       </c>
       <c r="R6" t="n">
-        <v>7029380</v>
+        <v>7029397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1278,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
+          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,12 +1287,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,7 +1331,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130158948</v>
+        <v>130158949</v>
       </c>
       <c r="B7" t="n">
         <v>91724</v>
@@ -1361,10 +1373,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499602</v>
+        <v>499788</v>
       </c>
       <c r="R7" t="n">
-        <v>7029397</v>
+        <v>7029153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,7 +1413,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
+          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,12 +1443,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1454,10 +1466,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130158949</v>
+        <v>130158947</v>
       </c>
       <c r="B8" t="n">
-        <v>91724</v>
+        <v>57007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,41 +1477,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499788</v>
+        <v>499666</v>
       </c>
       <c r="R8" t="n">
-        <v>7029153</v>
+        <v>7029380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1536,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
+          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,33 +1566,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1589,27 +1589,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130158946</v>
+        <v>130158941</v>
       </c>
       <c r="B9" t="n">
-        <v>57930</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,33 +1617,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499792</v>
+        <v>499782</v>
       </c>
       <c r="R9" t="n">
-        <v>7029121</v>
+        <v>7029157</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1680,7 +1672,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
+          <t>Grova äldre hackspår i en levande gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,7 +1686,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1712,27 +1724,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130158941</v>
+        <v>130158946</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1740,25 +1752,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499782</v>
+        <v>499792</v>
       </c>
       <c r="R10" t="n">
-        <v>7029157</v>
+        <v>7029121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1795,7 +1815,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Grova äldre hackspår i en levande gran.</t>
+          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,27 +1829,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130158960</v>
+        <v>130158961</v>
       </c>
       <c r="B14" t="n">
         <v>79180</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499700</v>
+        <v>499797</v>
       </c>
       <c r="R14" t="n">
-        <v>7029304</v>
+        <v>7029116</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2285,11 +2285,6 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2302,7 +2297,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2340,7 +2335,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130158961</v>
+        <v>130158960</v>
       </c>
       <c r="B15" t="n">
         <v>79180</v>
@@ -2378,10 +2373,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499797</v>
+        <v>499700</v>
       </c>
       <c r="R15" t="n">
-        <v>7029116</v>
+        <v>7029304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2416,6 +2411,11 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -2184,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130158961</v>
+        <v>130158960</v>
       </c>
       <c r="B14" t="n">
         <v>79180</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499797</v>
+        <v>499700</v>
       </c>
       <c r="R14" t="n">
-        <v>7029116</v>
+        <v>7029304</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2285,6 +2285,11 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2297,7 +2302,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2335,7 +2340,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130158960</v>
+        <v>130158961</v>
       </c>
       <c r="B15" t="n">
         <v>79180</v>
@@ -2373,10 +2378,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499700</v>
+        <v>499797</v>
       </c>
       <c r="R15" t="n">
-        <v>7029304</v>
+        <v>7029116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2411,11 +2416,6 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -1589,27 +1589,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130158941</v>
+        <v>130158946</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,25 +1617,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499782</v>
+        <v>499792</v>
       </c>
       <c r="R9" t="n">
-        <v>7029157</v>
+        <v>7029121</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1672,7 +1680,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Grova äldre hackspår i en levande gran.</t>
+          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,27 +1694,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1724,27 +1712,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130158946</v>
+        <v>130158941</v>
       </c>
       <c r="B10" t="n">
-        <v>57930</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1752,33 +1740,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499792</v>
+        <v>499782</v>
       </c>
       <c r="R10" t="n">
-        <v>7029121</v>
+        <v>7029157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1815,7 +1795,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
+          <t>Grova äldre hackspår i en levande gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1829,7 +1809,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130158947</v>
+        <v>130158948</v>
       </c>
       <c r="B6" t="n">
-        <v>57007</v>
+        <v>91724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,50 +1207,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499666</v>
+        <v>499602</v>
       </c>
       <c r="R6" t="n">
-        <v>7029380</v>
+        <v>7029397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1278,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
+          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,12 +1287,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,7 +1331,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130158948</v>
+        <v>130158949</v>
       </c>
       <c r="B7" t="n">
         <v>91724</v>
@@ -1361,10 +1373,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499602</v>
+        <v>499788</v>
       </c>
       <c r="R7" t="n">
-        <v>7029397</v>
+        <v>7029153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,7 +1413,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
+          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,12 +1443,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1454,10 +1466,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130158949</v>
+        <v>130158947</v>
       </c>
       <c r="B8" t="n">
-        <v>91724</v>
+        <v>57007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,41 +1477,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499788</v>
+        <v>499666</v>
       </c>
       <c r="R8" t="n">
-        <v>7029153</v>
+        <v>7029380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1536,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
+          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,33 +1566,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130158948</v>
+        <v>130158947</v>
       </c>
       <c r="B6" t="n">
-        <v>91724</v>
+        <v>57007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,41 +1207,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499602</v>
+        <v>499666</v>
       </c>
       <c r="R6" t="n">
-        <v>7029397</v>
+        <v>7029380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1287,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
+          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,33 +1296,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1331,7 +1319,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130158949</v>
+        <v>130158948</v>
       </c>
       <c r="B7" t="n">
         <v>91724</v>
@@ -1373,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499788</v>
+        <v>499602</v>
       </c>
       <c r="R7" t="n">
-        <v>7029153</v>
+        <v>7029397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,7 +1401,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
+          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,12 +1431,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1466,10 +1454,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130158947</v>
+        <v>130158949</v>
       </c>
       <c r="B8" t="n">
-        <v>57007</v>
+        <v>91724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,50 +1465,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499666</v>
+        <v>499788</v>
       </c>
       <c r="R8" t="n">
-        <v>7029380</v>
+        <v>7029153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1557,7 +1536,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
+          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,12 +1545,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1589,27 +1589,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130158946</v>
+        <v>130158941</v>
       </c>
       <c r="B9" t="n">
-        <v>57930</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,33 +1617,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499792</v>
+        <v>499782</v>
       </c>
       <c r="R9" t="n">
-        <v>7029121</v>
+        <v>7029157</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1680,7 +1672,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
+          <t>Grova äldre hackspår i en levande gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,7 +1686,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1712,27 +1724,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130158941</v>
+        <v>130158946</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1740,25 +1752,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499782</v>
+        <v>499792</v>
       </c>
       <c r="R10" t="n">
-        <v>7029157</v>
+        <v>7029121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1795,7 +1815,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Grova äldre hackspår i en levande gran.</t>
+          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,27 +1829,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158953</v>
       </c>
       <c r="B2" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130158954</v>
       </c>
       <c r="B3" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>130158951</v>
       </c>
       <c r="B4" t="n">
-        <v>98826</v>
+        <v>98829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130158952</v>
       </c>
       <c r="B5" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130158947</v>
+        <v>130158948</v>
       </c>
       <c r="B6" t="n">
-        <v>57007</v>
+        <v>91727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,50 +1207,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499666</v>
+        <v>499602</v>
       </c>
       <c r="R6" t="n">
-        <v>7029380</v>
+        <v>7029397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1278,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
+          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,12 +1287,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,10 +1331,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130158948</v>
+        <v>130158949</v>
       </c>
       <c r="B7" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,10 +1373,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499602</v>
+        <v>499788</v>
       </c>
       <c r="R7" t="n">
-        <v>7029397</v>
+        <v>7029153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,7 +1413,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
+          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,12 +1443,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1454,10 +1466,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130158949</v>
+        <v>130158947</v>
       </c>
       <c r="B8" t="n">
-        <v>91724</v>
+        <v>57007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,41 +1477,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499788</v>
+        <v>499666</v>
       </c>
       <c r="R8" t="n">
-        <v>7029153</v>
+        <v>7029380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1536,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
+          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,33 +1566,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1589,27 +1589,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130158941</v>
+        <v>130158946</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,25 +1617,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499782</v>
+        <v>499792</v>
       </c>
       <c r="R9" t="n">
-        <v>7029157</v>
+        <v>7029121</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1672,7 +1680,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Grova äldre hackspår i en levande gran.</t>
+          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,27 +1694,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1724,27 +1712,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130158946</v>
+        <v>130158941</v>
       </c>
       <c r="B10" t="n">
-        <v>57930</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1752,33 +1740,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499792</v>
+        <v>499782</v>
       </c>
       <c r="R10" t="n">
-        <v>7029121</v>
+        <v>7029157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1815,7 +1795,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
+          <t>Grova äldre hackspår i en levande gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1829,7 +1809,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
         <v>130158944</v>
       </c>
       <c r="B11" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130158961</v>
+        <v>130158960</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499797</v>
+        <v>499700</v>
       </c>
       <c r="R14" t="n">
-        <v>7029116</v>
+        <v>7029304</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2285,6 +2285,11 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2297,7 +2302,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2335,10 +2340,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130158960</v>
+        <v>130158961</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2373,10 +2378,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499700</v>
+        <v>499797</v>
       </c>
       <c r="R15" t="n">
-        <v>7029304</v>
+        <v>7029116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2411,11 +2416,6 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2469,7 +2469,7 @@
         <v>130158962</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>130158963</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158953</v>
       </c>
       <c r="B2" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130158954</v>
       </c>
       <c r="B3" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>130158951</v>
       </c>
       <c r="B4" t="n">
-        <v>98829</v>
+        <v>98855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130158952</v>
       </c>
       <c r="B5" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130158948</v>
+        <v>130158947</v>
       </c>
       <c r="B6" t="n">
-        <v>91727</v>
+        <v>57033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,41 +1207,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499602</v>
+        <v>499666</v>
       </c>
       <c r="R6" t="n">
-        <v>7029397</v>
+        <v>7029380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1287,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
+          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,33 +1296,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1331,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130158949</v>
+        <v>130158948</v>
       </c>
       <c r="B7" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499788</v>
+        <v>499602</v>
       </c>
       <c r="R7" t="n">
-        <v>7029153</v>
+        <v>7029397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,7 +1401,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
+          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,12 +1431,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1466,10 +1454,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130158947</v>
+        <v>130158949</v>
       </c>
       <c r="B8" t="n">
-        <v>57007</v>
+        <v>91753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,50 +1465,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499666</v>
+        <v>499788</v>
       </c>
       <c r="R8" t="n">
-        <v>7029380</v>
+        <v>7029153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1557,7 +1536,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
+          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,12 +1545,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1589,27 +1589,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130158946</v>
+        <v>130158941</v>
       </c>
       <c r="B9" t="n">
-        <v>57930</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,33 +1617,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499792</v>
+        <v>499782</v>
       </c>
       <c r="R9" t="n">
-        <v>7029121</v>
+        <v>7029157</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1680,7 +1672,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
+          <t>Grova äldre hackspår i en levande gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,7 +1686,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1712,27 +1724,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130158941</v>
+        <v>130158946</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57956</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1740,25 +1752,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499782</v>
+        <v>499792</v>
       </c>
       <c r="R10" t="n">
-        <v>7029157</v>
+        <v>7029121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1795,7 +1815,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Grova äldre hackspår i en levande gran.</t>
+          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,27 +1829,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
         <v>130158944</v>
       </c>
       <c r="B11" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>130158942</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>130158940</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130158960</v>
+        <v>130158961</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499700</v>
+        <v>499797</v>
       </c>
       <c r="R14" t="n">
-        <v>7029304</v>
+        <v>7029116</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2285,11 +2285,6 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2302,7 +2297,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2340,10 +2335,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130158961</v>
+        <v>130158960</v>
       </c>
       <c r="B15" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2378,10 +2373,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499797</v>
+        <v>499700</v>
       </c>
       <c r="R15" t="n">
-        <v>7029116</v>
+        <v>7029304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2416,6 +2411,11 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2469,7 +2469,7 @@
         <v>130158962</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>130158963</v>
       </c>
       <c r="B17" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158953</v>
       </c>
       <c r="B2" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130158954</v>
       </c>
       <c r="B3" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>130158951</v>
       </c>
       <c r="B4" t="n">
-        <v>98855</v>
+        <v>98856</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130158952</v>
       </c>
       <c r="B5" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130158947</v>
+        <v>130158948</v>
       </c>
       <c r="B6" t="n">
-        <v>57033</v>
+        <v>91754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,50 +1207,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499666</v>
+        <v>499602</v>
       </c>
       <c r="R6" t="n">
-        <v>7029380</v>
+        <v>7029397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1278,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
+          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,12 +1287,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,10 +1331,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130158948</v>
+        <v>130158949</v>
       </c>
       <c r="B7" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,10 +1373,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499602</v>
+        <v>499788</v>
       </c>
       <c r="R7" t="n">
-        <v>7029397</v>
+        <v>7029153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,7 +1413,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en granstubbe i granskog.</t>
+          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,12 +1443,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1454,10 +1466,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130158949</v>
+        <v>130158947</v>
       </c>
       <c r="B8" t="n">
-        <v>91753</v>
+        <v>57033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,41 +1477,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499788</v>
+        <v>499666</v>
       </c>
       <c r="R8" t="n">
-        <v>7029153</v>
+        <v>7029380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1536,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en grov döende gran med 56 cm i brösthöjdsdiameter i granskog.</t>
+          <t>Synobservation av minst 2 individer av järpe, födosökande och med både sångläte och varningsläte. Fyndplats i flerskiktad luckig granskog med inslag av björk och tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,33 +1566,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1589,27 +1589,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130158941</v>
+        <v>130158946</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57956</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,25 +1617,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499782</v>
+        <v>499792</v>
       </c>
       <c r="R9" t="n">
-        <v>7029157</v>
+        <v>7029121</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1672,7 +1680,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Grova äldre hackspår i en levande gran.</t>
+          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,27 +1694,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1724,27 +1712,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130158946</v>
+        <v>130158941</v>
       </c>
       <c r="B10" t="n">
-        <v>57956</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1752,33 +1740,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499792</v>
+        <v>499782</v>
       </c>
       <c r="R10" t="n">
-        <v>7029121</v>
+        <v>7029157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1815,7 +1795,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
+          <t>Grova äldre hackspår i en levande gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1829,7 +1809,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
         <v>130158944</v>
       </c>
       <c r="B11" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130158961</v>
+        <v>130158960</v>
       </c>
       <c r="B14" t="n">
         <v>79209</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499797</v>
+        <v>499700</v>
       </c>
       <c r="R14" t="n">
-        <v>7029116</v>
+        <v>7029304</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2285,6 +2285,11 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2297,7 +2302,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2335,7 +2340,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130158960</v>
+        <v>130158961</v>
       </c>
       <c r="B15" t="n">
         <v>79209</v>
@@ -2373,10 +2378,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499700</v>
+        <v>499797</v>
       </c>
       <c r="R15" t="n">
-        <v>7029304</v>
+        <v>7029116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2411,11 +2416,6 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">

--- a/artfynd/A 55039-2025 artfynd.xlsx
+++ b/artfynd/A 55039-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158953</v>
       </c>
       <c r="B2" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130158954</v>
       </c>
       <c r="B3" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>130158951</v>
       </c>
       <c r="B4" t="n">
-        <v>98856</v>
+        <v>98857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130158952</v>
       </c>
       <c r="B5" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>130158948</v>
       </c>
       <c r="B6" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>130158949</v>
       </c>
       <c r="B7" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1589,27 +1589,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130158946</v>
+        <v>130158941</v>
       </c>
       <c r="B9" t="n">
-        <v>57956</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,33 +1617,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499792</v>
+        <v>499782</v>
       </c>
       <c r="R9" t="n">
-        <v>7029121</v>
+        <v>7029157</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1680,7 +1672,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
+          <t>Grova äldre hackspår i en levande gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,7 +1686,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1712,27 +1724,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130158941</v>
+        <v>130158946</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>57956</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1740,25 +1752,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gremmelgård Väst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499782</v>
+        <v>499792</v>
       </c>
       <c r="R10" t="n">
-        <v>7029157</v>
+        <v>7029121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1795,7 +1815,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Grova äldre hackspår i en levande gran.</t>
+          <t>2 födosökande lavskrikor med lockläte i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,27 +1829,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
         <v>130158944</v>
       </c>
       <c r="B11" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
